--- a/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week05_28Sep.xlsx
+++ b/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week05_28Sep.xlsx
@@ -1131,7 +1131,7 @@
     <row r="8" ht="45.75" customHeight="1" s="47">
       <c r="A8" s="55" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: Black History Month launches (Thu 1 Oct, runs to W8) — Grow Humanities' Black British history/migration work carries it; PSHE's stereotype work lands next week.  National Poetry Day Thu 1 Oct (tbc).  EVIDENCE: display + EFL: cultural; log the BHM launch → log in the SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: Black History Month launches (Thu 1 Oct, runs to W8) — Grow Humanities' Black British history/migration work carries it; PSHE's stereotype work lands next week.  National Poetry Day Thu 1 Oct (tbc).  EVIDENCE: display + evidence platform: cultural; log the BHM launch → log in the SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="56" t="n"/>
@@ -1343,7 +1343,7 @@
 Targeted questioning to develop reasoning and operation selection skills.
 Ongoing assessment through observation, discussion and marked work.
 Positive feedback and opportunities for peer support and collaborative learning.
-LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily evidence platform].</t>
         </is>
       </c>
       <c r="J11" s="64" t="inlineStr">
@@ -1448,7 +1448,7 @@
       <c r="I13" s="64" t="inlineStr">
         <is>
           <t>TA shadows the freeze-frames and prompts the pause; teacher narrates the risk-naming step; the pocket cards go home — real transfer.
-LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to EFL, same day [E: PfA/citizenship/social enterprise — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to evidence platform, same day [E: PfA/citizenship/social enterprise — daily evidence platform].</t>
         </is>
       </c>
       <c r="J13" s="64" t="inlineStr">
